--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120512160</v>
+        <v>120513158</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617452</v>
+        <v>617408</v>
       </c>
       <c r="R2" t="n">
-        <v>6906980</v>
+        <v>6906795</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120514316</v>
+        <v>120511605</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +809,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617303</v>
+        <v>617494</v>
       </c>
       <c r="R3" t="n">
-        <v>6906584</v>
+        <v>6907149</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120513016</v>
+        <v>120511741</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +930,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617402</v>
+        <v>617463</v>
       </c>
       <c r="R4" t="n">
-        <v>6906834</v>
+        <v>6907077</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120511605</v>
+        <v>120513016</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,43 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617494</v>
+        <v>617402</v>
       </c>
       <c r="R5" t="n">
-        <v>6907149</v>
+        <v>6906834</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120512509</v>
+        <v>120514316</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1185,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617483</v>
+        <v>617303</v>
       </c>
       <c r="R6" t="n">
-        <v>6906973</v>
+        <v>6906584</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120512487</v>
+        <v>120512509</v>
       </c>
       <c r="B7" t="n">
-        <v>94550</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1284,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1355,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 nya kapslar, 3 från fjolåret. På kraftigt rötad, delvis sönderfallen granstubbe.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,26 +1377,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120513158</v>
+        <v>120512160</v>
       </c>
       <c r="B8" t="n">
-        <v>57341</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,36 +1405,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1467,13 +1442,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617408</v>
+        <v>617452</v>
       </c>
       <c r="R8" t="n">
-        <v>6906795</v>
+        <v>6906980</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1502,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120511741</v>
+        <v>120513161</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1574,7 +1549,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1588,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617463</v>
+        <v>617408</v>
       </c>
       <c r="R9" t="n">
-        <v>6907077</v>
+        <v>6906795</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1623,7 +1598,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1633,7 +1608,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1772,47 +1747,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120513161</v>
+        <v>120512487</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>94550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1821,10 +1796,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>617408</v>
+        <v>617483</v>
       </c>
       <c r="R11" t="n">
-        <v>6906795</v>
+        <v>6906973</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1856,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1866,7 +1841,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 nya kapslar, 3 från fjolåret. På kraftigt rötad, delvis sönderfallen granstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,6 +1857,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120513158</v>
+        <v>120511741</v>
       </c>
       <c r="B2" t="n">
-        <v>57341</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617408</v>
+        <v>617463</v>
       </c>
       <c r="R2" t="n">
-        <v>6906795</v>
+        <v>6907077</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120511605</v>
+        <v>120514316</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,35 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617494</v>
+        <v>617303</v>
       </c>
       <c r="R3" t="n">
-        <v>6907149</v>
+        <v>6906584</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120511741</v>
+        <v>120512509</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -953,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -967,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617463</v>
+        <v>617483</v>
       </c>
       <c r="R4" t="n">
-        <v>6907077</v>
+        <v>6906973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120513016</v>
+        <v>120511605</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1054,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617402</v>
+        <v>617494</v>
       </c>
       <c r="R5" t="n">
-        <v>6906834</v>
+        <v>6907149</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120514316</v>
+        <v>120512160</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,35 +1171,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617303</v>
+        <v>617452</v>
       </c>
       <c r="R6" t="n">
-        <v>6906584</v>
+        <v>6906980</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120512509</v>
+        <v>120513016</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,47 +1292,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617483</v>
+        <v>617402</v>
       </c>
       <c r="R7" t="n">
-        <v>6906973</v>
+        <v>6906834</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120512160</v>
+        <v>120513158</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,35 +1404,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617452</v>
+        <v>617408</v>
       </c>
       <c r="R8" t="n">
-        <v>6906980</v>
+        <v>6906795</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120513161</v>
+        <v>120511816</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,47 +1526,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617408</v>
+        <v>617473</v>
       </c>
       <c r="R9" t="n">
-        <v>6906795</v>
+        <v>6907016</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1598,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1608,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120511816</v>
+        <v>120513161</v>
       </c>
       <c r="B10" t="n">
-        <v>78576</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,38 +1638,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617473</v>
+        <v>617408</v>
       </c>
       <c r="R10" t="n">
-        <v>6907016</v>
+        <v>6906795</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,6 +1891,118 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125506813</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91180</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergebäcken, Bergebäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>617528</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6907151</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1896,12 +1896,7 @@
         <v>125506813</v>
       </c>
       <c r="B12" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1896,7 +1896,7 @@
         <v>125506813</v>
       </c>
       <c r="B12" t="n">
-        <v>91234</v>
+        <v>91241</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1896,7 +1896,7 @@
         <v>125506813</v>
       </c>
       <c r="B12" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1896,7 +1896,7 @@
         <v>125506813</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>91246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1896,7 +1896,7 @@
         <v>125506813</v>
       </c>
       <c r="B12" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1896,7 +1896,7 @@
         <v>125506813</v>
       </c>
       <c r="B12" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,6 +1998,225 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128354132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95921</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>210</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergebäcken, Bergebäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>617527</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6907148</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 gammal kapsel. På murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128354311</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92673</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergebäcken, Bergebäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>617503</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6906993</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>128354132</v>
       </c>
       <c r="B13" t="n">
-        <v>95921</v>
+        <v>95926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128354311</v>
       </c>
       <c r="B14" t="n">
-        <v>92673</v>
+        <v>92678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>128354132</v>
       </c>
       <c r="B13" t="n">
-        <v>95926</v>
+        <v>96019</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128354311</v>
       </c>
       <c r="B14" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>128354132</v>
       </c>
       <c r="B13" t="n">
-        <v>96019</v>
+        <v>96031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128354311</v>
       </c>
       <c r="B14" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>128354132</v>
       </c>
       <c r="B13" t="n">
-        <v>96031</v>
+        <v>96033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128354311</v>
       </c>
       <c r="B14" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>128354132</v>
       </c>
       <c r="B13" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128354311</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>128354132</v>
       </c>
       <c r="B13" t="n">
-        <v>96034</v>
+        <v>96061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128354311</v>
       </c>
       <c r="B14" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120512509</v>
+        <v>120511816</v>
       </c>
       <c r="B2" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617483</v>
+        <v>617473</v>
       </c>
       <c r="R2" t="n">
-        <v>6906973</v>
+        <v>6907016</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120511605</v>
+        <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>100320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,31 +793,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617494</v>
+        <v>617483</v>
       </c>
       <c r="R3" t="n">
-        <v>6907149</v>
+        <v>6906973</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 nya kapslar, 3 från fjolåret. På kraftigt rötad, delvis sönderfallen granstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +887,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,15 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120511816</v>
+        <v>120512160</v>
       </c>
       <c r="B4" t="n">
-        <v>78628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +934,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617473</v>
+        <v>617452</v>
       </c>
       <c r="R4" t="n">
-        <v>6907016</v>
+        <v>6906980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,47 +1039,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120513161</v>
+        <v>120513197</v>
       </c>
       <c r="B5" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1078,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617408</v>
+        <v>617442</v>
       </c>
       <c r="R5" t="n">
-        <v>6906795</v>
+        <v>6906806</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1128,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stor häxring med många fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,63 +1160,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120513158</v>
+        <v>120513016</v>
       </c>
       <c r="B6" t="n">
-        <v>57369</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100110</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617408</v>
+        <v>617402</v>
       </c>
       <c r="R6" t="n">
-        <v>6906795</v>
+        <v>6906834</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,47 +1267,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120514316</v>
+        <v>120513158</v>
       </c>
       <c r="B7" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1321,13 +1312,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617303</v>
+        <v>617408</v>
       </c>
       <c r="R7" t="n">
-        <v>6906584</v>
+        <v>6906795</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,50 +1384,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120513016</v>
+        <v>120512509</v>
       </c>
       <c r="B8" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617402</v>
+        <v>617483</v>
       </c>
       <c r="R8" t="n">
-        <v>6906834</v>
+        <v>6906973</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,47 +1500,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120512160</v>
+        <v>120513161</v>
       </c>
       <c r="B9" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1554,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617452</v>
+        <v>617408</v>
       </c>
       <c r="R9" t="n">
-        <v>6906980</v>
+        <v>6906795</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,15 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120511741</v>
+        <v>120513204</v>
       </c>
       <c r="B10" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1646,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1675,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617463</v>
+        <v>617443</v>
       </c>
       <c r="R10" t="n">
-        <v>6907077</v>
+        <v>6906806</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,47 +1732,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120512487</v>
+        <v>120514316</v>
       </c>
       <c r="B11" t="n">
-        <v>94673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1796,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>617483</v>
+        <v>617303</v>
       </c>
       <c r="R11" t="n">
-        <v>6906973</v>
+        <v>6906584</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,12 +1821,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 nya kapslar, 3 från fjolåret. På kraftigt rötad, delvis sönderfallen granstubbe.</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,26 +1832,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1893,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125506813</v>
+        <v>128354132</v>
       </c>
       <c r="B12" t="n">
-        <v>91250</v>
+        <v>96554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1928,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>617528</v>
+        <v>617527</v>
       </c>
       <c r="R12" t="n">
-        <v>6907151</v>
+        <v>6907148</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,22 +1913,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 gammal kapsel. På murken granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,32 +1960,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128354132</v>
+        <v>125506813</v>
       </c>
       <c r="B13" t="n">
-        <v>96078</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2035,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>617527</v>
+        <v>617528</v>
       </c>
       <c r="R13" t="n">
-        <v>6907148</v>
+        <v>6907151</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2065,27 +2025,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 gammal kapsel. På murken granlåga.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,36 +2067,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128354311</v>
+        <v>120511521</v>
       </c>
       <c r="B14" t="n">
-        <v>92827</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>617503</v>
+        <v>617561</v>
       </c>
       <c r="R14" t="n">
-        <v>6906993</v>
+        <v>6907156</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2168,22 +2141,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,6 +2180,238 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120511741</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergebäcken, Bergebäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>617463</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6907077</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120511605</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergebäcken, Bergebäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>617494</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6907149</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511816</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354132</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512160</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125506813</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513016</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511521</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513158</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511741</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120512509</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513161</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513204</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2296,6 +2366,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120514316</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2412,8 +2487,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120511605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
